--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,347 @@
           <t>Kontinuitetsskogar Gyllbergens skogsrike</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127760319</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lortån, Lortån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>508359</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6703419</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127759676</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Abborrviken, Abborrviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>508200</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6703260</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127759327</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Abborrviken, Abborrviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508249</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6703324</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127760319</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127759676</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127759327</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127760319</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127759676</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127759327</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127760319</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127759676</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127759327</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,7 +794,7 @@
         <v>127760319</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>127759676</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127759327</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,6 +1129,460 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128499950</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lortån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508251</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6703489</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128500434</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lortån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>508251</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6703489</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128501463</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lortån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>508251</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6703489</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128502743</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92736</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lortån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>508251</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6703489</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,31 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,26 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1206,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,31 +1259,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92760</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,31 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92748</v>
+        <v>92766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,26 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1206,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92768</v>
+        <v>92756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,31 +1259,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,31 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,26 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1206,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92796</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,31 +1259,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97496</v>
+        <v>97502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97502</v>
+        <v>97509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,31 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,26 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1206,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,31 +1259,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,31 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,26 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1206,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B7" t="n">
-        <v>92810</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,31 +1259,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,31 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38277-2025 artfynd.xlsx
+++ b/artfynd/A 38277-2025 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128499950</v>
+        <v>128500434</v>
       </c>
       <c r="B6" t="n">
-        <v>92818</v>
+        <v>92811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,31 +1143,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1211,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128500434</v>
+        <v>128499950</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,7 +1362,7 @@
         <v>128501463</v>
       </c>
       <c r="B8" t="n">
-        <v>97523</v>
+        <v>97528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128502743</v>
       </c>
       <c r="B9" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
